--- a/www/download/IND.surplus_value.empe_ms.r.pc.WIOD13.xlsx
+++ b/www/download/IND.surplus_value.empe_ms.r.pc.WIOD13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>0.580193949583964</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>0.551293995707052</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>0.61714750825961</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.74</t>
+          <t>0.627410728680112</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>0.532584382102609</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.645310091935677</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>0.700533768016288</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>0.641913281751535</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>55.91</t>
+          <t>0.559247479502945</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>0.365056087165048</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>0.307476020224686</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>0.341347361773246</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>0.31643883611631</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>45.46</t>
+          <t>0.454571011552628</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>51.67</t>
+          <t>0.516750565970197</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0.0567310662891023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>0.102443709161079</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29.69</t>
+          <t>0.296934163903501</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>0.277028924183672</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>0.259427206301593</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>0.339029281863222</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>0.325630445508075</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>0.324414309276383</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>0.265097656861603</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>0.202879587830145</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>0.180310005716608</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>16.22</t>
+          <t>0.162210984513704</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>0.160163818636401</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>0.214390888563969</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>0.310793460583662</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-16.6</t>
+          <t>-0.165896409948928</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-0.182127230793031</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-14.17</t>
+          <t>-0.14166432327897</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>-0.135540093135258</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-20.39</t>
+          <t>-0.216755039543478</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-0.224588257257891</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-26.66</t>
+          <t>-0.266524360186788</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>-0.322453427467491</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-42.6</t>
+          <t>-0.42591877027464</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-46.68</t>
+          <t>-0.466818026877302</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-45.48</t>
+          <t>-0.454815796092454</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-44.35</t>
+          <t>-0.443482975419388</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-41.91</t>
+          <t>-0.41903588271488</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-34.63</t>
+          <t>-0.34631538097527</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-37.88</t>
+          <t>-0.378796539020013</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>232.89</t>
+          <t>2.32908872680117</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>281.54</t>
+          <t>2.81553552230419</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>336.9</t>
+          <t>3.36911651662052</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>227.74</t>
+          <t>2.27735111979551</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>257.7</t>
+          <t>2.50311503150162</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>267.76</t>
+          <t>2.67776206284326</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>253.65</t>
+          <t>2.53669857210618</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>272.62</t>
+          <t>2.72654874597587</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>410.1</t>
+          <t>4.10125585196181</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>283.18</t>
+          <t>2.83169680788901</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>297.91</t>
+          <t>2.97919726013345</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>313.23</t>
+          <t>3.13265623068728</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>311.47</t>
+          <t>3.1149905784815</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>283.45</t>
+          <t>2.83428041494853</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>248.14</t>
+          <t>2.4814563073618</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>117.84</t>
+          <t>1.17858707750664</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>130.24</t>
+          <t>1.30251919146435</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>1.52511501261685</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>159.77</t>
+          <t>1.59771111756882</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>194.86</t>
+          <t>1.88568283759216</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>219.05</t>
+          <t>2.19070682715091</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>244.58</t>
+          <t>2.44618880165921</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>269.17</t>
+          <t>2.69216485615695</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>287.88</t>
+          <t>2.8788607730228</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>290.37</t>
+          <t>2.90360862211601</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>281.26</t>
+          <t>2.81277665301742</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>291.68</t>
+          <t>2.917064466723</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>303.18</t>
+          <t>3.0322678803258</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>300.29</t>
+          <t>3.0029891269742</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>310.69</t>
+          <t>3.10706567646685</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>0.918807318409685</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>103.17</t>
+          <t>1.03204290494135</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>118.51</t>
+          <t>1.18546827930848</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>105.67</t>
+          <t>1.05668321575633</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>0.937593515244086</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>82.43</t>
+          <t>0.824425054296779</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>73.08</t>
+          <t>0.731267518060251</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>0.743473056580311</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>63.24</t>
+          <t>0.632529172589637</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>0.579622842163958</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>0.466567940564514</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>0.42348901666551</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>0.490838465444092</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>0.518061510811641</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>0.641139070251585</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-39.43</t>
+          <t>-0.394311733438367</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-35.51</t>
+          <t>-0.355066671832782</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-0.353128095004113</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-34.22</t>
+          <t>-0.342242345341239</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-32.95</t>
+          <t>-0.342746156174521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-29.77</t>
+          <t>-0.29773538297535</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-0.223042270281474</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>-0.175193286788704</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-0.104604973547073</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.0106953736001085</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>0.056201979948723</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>0.0932611132631467</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>0.25230137348249</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>0.291737770811354</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>0.341715572532232</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>112.89</t>
+          <t>1.12912026704838</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>1.0750064179935</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>137.07</t>
+          <t>1.37082719674942</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>127.4</t>
+          <t>1.27400667923295</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>110.77</t>
+          <t>1.06963846717267</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>117.72</t>
+          <t>1.17742259222568</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>96.63</t>
+          <t>0.966595783094154</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>93.97</t>
+          <t>0.940005540921056</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>0.77286973327843</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>81.12</t>
+          <t>0.811209425453014</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>0.838961691808536</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>0.925905320250997</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>116.66</t>
+          <t>1.16685272736336</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>89.85</t>
+          <t>0.898464122391809</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>132.37</t>
+          <t>1.32383170165371</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>391.6</t>
+          <t>3.91751869350779</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>244.92</t>
+          <t>2.44928223291742</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>271.43</t>
+          <t>2.71438299820255</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>265.15</t>
+          <t>2.65137146232832</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>269.42</t>
+          <t>2.65735563543749</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>286.15</t>
+          <t>2.86161526637351</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>253.22</t>
+          <t>2.53233149803632</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>240.91</t>
+          <t>2.40956761606521</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>210.37</t>
+          <t>2.10391727225272</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>192.62</t>
+          <t>1.9260516738534</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>184.54</t>
+          <t>1.84547027913159</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>196.81</t>
+          <t>1.96822637695465</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>192.94</t>
+          <t>1.92974540910067</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>199.16</t>
+          <t>1.99168247563141</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>247.28</t>
+          <t>2.47285504090424</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-0.0295326512378432</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>0.0673428256465038</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>0.214698037214987</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>0.193332598518116</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>0.133665596168653</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>0.09644559927637</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>0.124081034548847</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13.86</t>
+          <t>0.139194636687895</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.00601377266718028</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.0190694751676951</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.0236484530394316</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>0.0343809018820866</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.0306095300754696</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>0.0973205976923597</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>14.44</t>
+          <t>0.144456318724835</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-0.13922791975748</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-0.11645008539367</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>0.159735979917159</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>0.0695605924218721</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.0499509027950769</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>0.126287350700115</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>0.0866166654090192</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>0.0486316408103813</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-9.71</t>
+          <t>-0.0970488870586572</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-0.100283664151297</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-0.101364093238597</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-0.109350756388247</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>-0.102924372656117</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.0326247815496727</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>0.0804138355871742</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>56.25</t>
+          <t>0.562783094387642</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>67.21</t>
+          <t>0.672289862615998</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>99.45</t>
+          <t>0.99461486380043</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>84.29</t>
+          <t>0.842844177113651</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>75.81</t>
+          <t>0.730439913212519</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>80.78</t>
+          <t>0.807997274085597</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>0.723667400588436</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>65.66</t>
+          <t>0.656785032487658</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>63.22</t>
+          <t>0.632343257704203</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>0.448902691927986</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>0.435605231664819</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>0.408358077170848</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>0.440713144836427</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>0.472181674699172</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>65.34</t>
+          <t>0.653458617474893</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>396.37</t>
+          <t>3.96445870352701</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>357.59</t>
+          <t>3.57660166595455</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>334.59</t>
+          <t>3.34618355634921</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>306.42</t>
+          <t>3.0642741199111</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>322.95</t>
+          <t>3.16430529316012</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>263.84</t>
+          <t>2.63897847087112</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>251.67</t>
+          <t>2.51785561908581</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>183.26</t>
+          <t>1.83300684471784</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>140.11</t>
+          <t>1.40189574530336</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>132.35</t>
+          <t>1.3245368691604</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>155.77</t>
+          <t>1.5578582012179</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>161.9</t>
+          <t>1.61951554884636</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>143.14</t>
+          <t>1.43168521877227</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>123.55</t>
+          <t>1.23571375474286</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>131.63</t>
+          <t>1.31650106722806</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>0.463585608356725</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>0.435301363747891</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>0.713315957089828</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>0.604996357539609</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>61.06</t>
+          <t>0.591134989992153</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>78.31</t>
+          <t>0.784950097244735</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>0.721629137501772</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>0.706844696190006</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>0.523097845791978</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>0.484432240287087</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>0.464709057215398</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>0.424557910323963</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>0.467712794550758</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>0.522950867657099</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>62.59</t>
+          <t>0.625997138360265</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>0.3509732103737</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>36.57</t>
+          <t>0.365810295734021</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>0.567782135675087</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>0.434966723889328</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>0.326688663823179</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>0.356544496357264</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>0.294738960493423</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>0.227953130361198</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>0.163049338373863</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>0.0906338827771398</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>0.08533102370366</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>0.104351627055332</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>0.132076938294274</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>0.1871964196578</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>0.296537125331889</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>66.35</t>
+          <t>0.66357581396995</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>0.67703651553952</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.82</t>
+          <t>0.808198976025105</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>67.66</t>
+          <t>0.676534459826351</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>0.567941851687406</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>54.95</t>
+          <t>0.549718886498035</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>0.477719405382432</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>0.441679361846805</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0.351598820970313</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>0.277393374197773</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>0.288653801702946</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>0.284666668152845</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>0.32421853191313</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>51.98</t>
+          <t>0.519863390954081</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>62.91</t>
+          <t>0.629200248856359</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>192.4</t>
+          <t>1.9240207773823</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>173.26</t>
+          <t>1.73269637401307</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>177.71</t>
+          <t>1.77710974092473</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>179.74</t>
+          <t>1.79741308742437</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>157.76</t>
+          <t>1.55597443501988</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>141.31</t>
+          <t>1.41311689462062</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>159.04</t>
+          <t>1.590645250341</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>130.61</t>
+          <t>1.30648235173961</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>137.37</t>
+          <t>1.37384822400886</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>129.51</t>
+          <t>1.29524455349697</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>135.1</t>
+          <t>1.3507186245292</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>1.31910670244334</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>117.86</t>
+          <t>1.17880763561891</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>121.76</t>
+          <t>1.21789036879972</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>116.88</t>
+          <t>1.16894420811545</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>193.02</t>
+          <t>1.93074884610254</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>206.77</t>
+          <t>2.06813853499745</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>230.71</t>
+          <t>2.30749134303039</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>238.77</t>
+          <t>2.3876346466763</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>241.82</t>
+          <t>2.33201852767592</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>233.55</t>
+          <t>2.33586332628373</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>251.96</t>
+          <t>2.52018322559879</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>230.2</t>
+          <t>2.30277440975128</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>221.31</t>
+          <t>2.21359066733505</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>268.67</t>
+          <t>2.68651331436467</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>279.52</t>
+          <t>2.79551302055475</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>301.77</t>
+          <t>3.01823910515369</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>291.28</t>
+          <t>2.91348390312581</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>327.47</t>
+          <t>3.27496558760288</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>365.53</t>
+          <t>3.65547316726745</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>0.696580897076219</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>0.882073432178093</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>104.71</t>
+          <t>1.04717143694109</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>133.15</t>
+          <t>1.3314843551471</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>146.91</t>
+          <t>1.45596280560652</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>130.48</t>
+          <t>1.30481959294985</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>115.17</t>
+          <t>1.15174306780471</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>100.19</t>
+          <t>1.00195368130878</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>0.894883176871307</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>0.788759087502419</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>81.83</t>
+          <t>0.818299858877784</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>0.906222451378153</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>83.42</t>
+          <t>0.834188970319828</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>0.883547376232908</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>0.881296914920459</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.0174327553305895</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>0.0882944980088485</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.0494517042231566</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>0.0671924130129125</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>0.0902297885942545</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>0.158794287488627</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>0.193887612209035</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>0.278691797994522</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>0.268942284738864</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>26.01</t>
+          <t>0.260147369398629</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>0.224819905110637</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>0.191787032912249</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>0.23162943538132</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>0.282703852771802</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>0.235358704104227</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>62.19</t>
+          <t>0.622401951819617</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>0.590477662587837</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.24</t>
+          <t>0.822593503312852</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>0.906388370632351</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>0.88693950502242</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>0.888615523831315</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>0.72190344480509</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>0.631800025148047</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>83.57</t>
+          <t>0.835922144292176</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>94.04</t>
+          <t>0.940405402043573</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>0.857272029022559</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>95.25</t>
+          <t>0.95257580797026</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>0.847609850337369</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>0.723999953552076</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>56.24</t>
+          <t>0.562456067410611</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>50.81</t>
+          <t>0.508490192899046</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>53.14</t>
+          <t>0.531952392232331</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>66.48</t>
+          <t>0.665142298069436</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>0.658322749846426</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>65.55</t>
+          <t>0.639634560474144</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0.70191034810142</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>0.564846896232953</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>0.502424616318313</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>48.43</t>
+          <t>0.484527968121209</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>0.279235564898311</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>0.267520995669403</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>0.24528342484992</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>0.305708643351056</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>0.434509239868747</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>0.588335539876957</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>0.398345609070897</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>0.595479810659402</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>77.38</t>
+          <t>0.774269773456837</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>84.49</t>
+          <t>0.844922955613975</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>0.71078393497904</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>64.06</t>
+          <t>0.640531283957104</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>0.674971051800675</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>0.768564097751425</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>71.96</t>
+          <t>0.720330950191541</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>0.642344924628324</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>62.91</t>
+          <t>0.629883732180749</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>71.42</t>
+          <t>0.713414291552791</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>0.893311074923461</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>94.62</t>
+          <t>0.946478455533957</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>87.16</t>
+          <t>0.870521666249317</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>100.35</t>
+          <t>1.00379363292628</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>104.61</t>
+          <t>1.0463781165663</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>125.55</t>
+          <t>1.25571092560575</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>153.78</t>
+          <t>1.53777023104975</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>162.25</t>
+          <t>1.5749187612181</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>149.42</t>
+          <t>1.49446196846496</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>157.28</t>
+          <t>1.57347622778517</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>149.71</t>
+          <t>1.49779794709675</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>133.49</t>
+          <t>1.33515176442308</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>133.45</t>
+          <t>1.33458365304332</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>134.97</t>
+          <t>1.34989658122701</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>127.84</t>
+          <t>1.27855570295368</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>131.85</t>
+          <t>1.31885765384974</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>153.63</t>
+          <t>1.53603872456038</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>168.79</t>
+          <t>1.68788362417922</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>306.07</t>
+          <t>3.06027465507252</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>284.7</t>
+          <t>2.84663940739435</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>287.31</t>
+          <t>2.87345853669205</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>233.83</t>
+          <t>2.33841236940722</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>217.66</t>
+          <t>2.14344400577835</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>218.3</t>
+          <t>2.18293472902094</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>217.31</t>
+          <t>2.1735227803873</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>210.31</t>
+          <t>2.10347175878059</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>176.42</t>
+          <t>1.76374540896733</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>228.06</t>
+          <t>2.28040446059128</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>223.35</t>
+          <t>2.23408352212606</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>214.1</t>
+          <t>2.14162906228779</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>225.86</t>
+          <t>2.2588873727566</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>213.6</t>
+          <t>2.13595018255971</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>230.46</t>
+          <t>2.3046411836572</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-0.0364075218334058</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>0.121771369491494</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>0.349107009535986</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>0.411413071685843</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>0.355441392003591</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>0.383383861694745</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>51.06</t>
+          <t>0.510644169064885</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>0.421972881542402</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>0.438212593601256</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.393740986104761</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>0.369486265332193</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>0.388106244335341</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>60.45</t>
+          <t>0.604989260665206</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>44.39</t>
+          <t>0.443946024572109</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>79.62</t>
+          <t>0.796321844688341</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>336.66</t>
+          <t>3.36724596918156</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>298.26</t>
+          <t>2.98305602232086</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>312.96</t>
+          <t>3.12987616644286</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>312.47</t>
+          <t>3.12468984415621</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>313.42</t>
+          <t>3.08920359893366</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>382.34</t>
+          <t>3.82394063692659</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>385.77</t>
+          <t>3.85848830277299</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>404.4</t>
+          <t>4.04460261673412</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>371.19</t>
+          <t>3.71226418642965</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>381.77</t>
+          <t>3.81774827894328</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>354.36</t>
+          <t>3.54385303146236</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>321.77</t>
+          <t>3.21829785498481</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>270.26</t>
+          <t>2.70307161047368</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>247.42</t>
+          <t>2.4737853791288</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>311.6</t>
+          <t>3.1160030512302</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>218.78</t>
+          <t>2.18802592810179</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>234.78</t>
+          <t>2.34795894461299</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>268.12</t>
+          <t>2.68141942436133</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>242.66</t>
+          <t>2.42652586988329</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>227.46</t>
+          <t>2.20805505814781</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>221.05</t>
+          <t>2.21063813101176</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>193.42</t>
+          <t>1.93480076660728</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>198.35</t>
+          <t>1.98418068280123</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>205.12</t>
+          <t>2.05138507698332</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>225.88</t>
+          <t>2.25885764302582</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>230.07</t>
+          <t>2.30087057369342</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>255.8</t>
+          <t>2.55829722249958</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>269.09</t>
+          <t>2.69130841250002</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>274.55</t>
+          <t>2.74543474829787</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>277.45</t>
+          <t>2.77454934757394</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>121.98</t>
+          <t>1.22007812922352</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>108.3</t>
+          <t>1.08323291572656</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>152.46</t>
+          <t>1.52485371780442</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>132.42</t>
+          <t>1.32413348515073</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>105.19</t>
+          <t>1.01495468403701</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>93.47</t>
+          <t>0.934892346590012</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0.462168693208995</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>62.91</t>
+          <t>0.629352583073705</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>0.918455416493603</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>89.63</t>
+          <t>0.896277009039295</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>0.905519303717878</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>1.00453538622117</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>93.16</t>
+          <t>0.93189794982559</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>0.853080566854119</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>111.05</t>
+          <t>1.11051921296029</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-27.2</t>
+          <t>-0.271944830924281</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>-0.236926467021793</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>0.127310511204593</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-0.0708628140663561</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>-0.111119300595284</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.0637825633891869</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-15.09</t>
+          <t>-0.150890688713446</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-23.19</t>
+          <t>-0.231872779741314</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-17.74</t>
+          <t>-0.177402562976904</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-19.22</t>
+          <t>-0.192236706748269</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-15.88</t>
+          <t>-0.158768109809997</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-0.159355952249213</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-0.169934103001088</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-18.51</t>
+          <t>-0.185068296675263</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-15.2</t>
+          <t>-0.151967115236042</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>101.2</t>
+          <t>1.01212452796774</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>0.899305809040175</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>0.884155729088635</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>0.826950893562085</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>0.962926591605485</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1.11005859366218</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>173.63</t>
+          <t>1.73653171251978</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>187.65</t>
+          <t>1.87680860427765</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>203.26</t>
+          <t>2.03278346635967</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>228.78</t>
+          <t>2.28778260852392</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>218.64</t>
+          <t>2.1865859622178</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>230.14</t>
+          <t>2.30176318177563</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>236.03</t>
+          <t>2.3607220070519</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>216.16</t>
+          <t>2.16166352634629</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>250.28</t>
+          <t>2.50286638926958</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>0.608932753463588</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>58.36</t>
+          <t>0.583696807281135</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>0.809023118826459</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>62.88</t>
+          <t>0.628810056092376</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>0.666803205616628</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>0.686797033380673</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>0.613953829703274</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>65.33</t>
+          <t>0.653502598986628</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>119.71</t>
+          <t>1.19722268367514</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>0.701511834803594</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>0.741769205203032</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>97.99</t>
+          <t>0.980008382349164</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>1.03512338792936</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>99.78</t>
+          <t>0.997775870596716</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>135.95</t>
+          <t>1.35958322470447</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>98.57</t>
+          <t>0.985783588201604</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>109.1</t>
+          <t>1.0910210665077</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>1.26012547711603</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>86.79</t>
+          <t>0.867856713022716</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>0.796580783039258</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>56.16</t>
+          <t>0.561603393052432</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>51.62</t>
+          <t>0.51628002303329</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>107.54</t>
+          <t>1.07557647947669</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>187.11</t>
+          <t>1.87118263324307</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>148.78</t>
+          <t>1.48773885149996</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>1.24405940925747</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>134.05</t>
+          <t>1.34092158042089</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>1.21754722847264</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>110.81</t>
+          <t>1.10782231317466</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>136.05</t>
+          <t>1.36049324827756</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>121.38</t>
+          <t>1.21390549221935</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>1.10009329017056</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>131.26</t>
+          <t>1.31262706376894</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>145.11</t>
+          <t>1.45110874865096</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>161.66</t>
+          <t>1.60007041079545</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>135.11</t>
+          <t>1.35118813063254</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>144.39</t>
+          <t>1.44404422334562</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>140.25</t>
+          <t>1.40261795235208</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>122.49</t>
+          <t>1.22493218777825</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>114.99</t>
+          <t>1.14983958732803</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>110.88</t>
+          <t>1.10880939227372</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>114.16</t>
+          <t>1.14178522031321</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>0.950233908397757</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>71.44</t>
+          <t>0.714216507178814</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>71.59</t>
+          <t>0.715943917172743</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>444.11</t>
+          <t>4.44177111297016</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>411.67</t>
+          <t>4.11704604632094</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>427.06</t>
+          <t>4.27107290262592</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>420.11</t>
+          <t>4.20103720390885</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>456.98</t>
+          <t>4.48360227367177</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>445.74</t>
+          <t>4.45767206859568</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>429.14</t>
+          <t>4.29227769960069</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>414.04</t>
+          <t>4.14122425552155</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>350.69</t>
+          <t>3.50681587681526</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>273.61</t>
+          <t>2.73592722599558</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>284.81</t>
+          <t>2.84846021479049</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>263.39</t>
+          <t>2.63400691056803</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>203.52</t>
+          <t>2.03450233329321</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>218.23</t>
+          <t>2.18203148308136</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>162.86</t>
+          <t>1.62863203733373</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>66.17</t>
+          <t>0.662132706079837</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>0.717073227421013</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>0.929347644302604</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>0.831052065147014</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>83.32</t>
+          <t>0.803415885768747</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>0.909150843848963</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>80.78</t>
+          <t>0.807617592979333</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>81.59</t>
+          <t>0.816042409507105</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>66.77</t>
+          <t>0.667772768028339</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>77.34</t>
+          <t>0.773068226565887</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>85.97</t>
+          <t>0.859445689406833</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>0.862129884306843</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>92.33</t>
+          <t>0.923622860019522</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>0.416913558217842</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>0.46138902026927</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>0.346904743100668</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>0.312777359244818</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>0.513239888464136</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>0.406328720631713</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>0.384289987547236</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>0.311662853255233</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>0.304731871068014</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>0.258313990142936</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>0.165730965940721</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>0.13143244475089</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.102704772911464</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>0.112198175284256</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>0.0907789461492841</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>0.239481484557031</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>0.40739246521588</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>152.49</t>
+          <t>1.52499727758562</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>129.35</t>
+          <t>1.29359644151237</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>126.08</t>
+          <t>1.26095522673005</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>125.23</t>
+          <t>1.25223740922421</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>106.17</t>
+          <t>1.02865918777167</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>1.48009636193902</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>170.16</t>
+          <t>1.70186208295219</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>221.99</t>
+          <t>2.22029194061551</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>217.58</t>
+          <t>2.17592844322955</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>189.94</t>
+          <t>1.89939841153863</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>209.49</t>
+          <t>2.09492976010666</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>224.36</t>
+          <t>2.24388976737693</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>221.61</t>
+          <t>2.2164431821064</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>0.896186765749718</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>115.17</t>
+          <t>1.15174470913216</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>65.82</t>
+          <t>0.658466713306814</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>0.566750413196724</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>77.76</t>
+          <t>0.777843706256315</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>0.862645967211306</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>91.99</t>
+          <t>0.886199990059886</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>83.97</t>
+          <t>0.839830805524183</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>79.95</t>
+          <t>0.800020740265699</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>85.62</t>
+          <t>0.856752680302644</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>86.65</t>
+          <t>0.866673135948963</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>0.909688851504248</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>94.21</t>
+          <t>0.942329047656411</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>103.63</t>
+          <t>1.03630103560097</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>129.01</t>
+          <t>1.29038330684844</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>133.65</t>
+          <t>1.33658428574489</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>158.89</t>
+          <t>1.5889209724758</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>0.981989746065783</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>102.71</t>
+          <t>1.02764358583863</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>105.3</t>
+          <t>1.05358312395379</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>95.75</t>
+          <t>0.957538389190901</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>0.872968044385012</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>0.766376710005381</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>70.04</t>
+          <t>0.700893122731219</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>0.641749600399432</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>0.593194978322952</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>0.589822910553466</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>0.583993138681663</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>64.96</t>
+          <t>0.649586095230487</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>0.757342941051712</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>88.71</t>
+          <t>0.886892353559466</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>94.39</t>
+          <t>0.943932294538396</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-0.0831734803123937</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-0.0181631408808801</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.0234295977918603</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-0.0269171171654012</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.0416035416227656</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-0.0320492839717326</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.017831562381413</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.00656075454821736</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>0.0684434725786285</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>0.135084845454851</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>0.130466398271813</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>0.139311293809424</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0.249015319004881</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>0.296075216105855</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>0.345488464629642</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>0.125739368162822</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>0.1838925446002</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>0.201254762673743</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>19.87</t>
+          <t>0.198654957643288</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>0.183512399926467</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>0.197463026954038</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>0.21687233213881</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>0.234949259752211</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>0.268819743344446</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>0.31066210067262</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>0.319681702656073</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>0.341702702414348</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>0.437933718670193</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0.478124394288923</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.513523940269115</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
